--- a/stories/arbres/ATOM-EMO.LEX.009-05.xlsx
+++ b/stories/arbres/ATOM-EMO.LEX.009-05.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B29"/>
+  <dimension ref="A1:B30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -602,7 +602,6 @@
           <t>secondary_lessons</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -819,6 +818,18 @@
       <c r="B29" t="inlineStr">
         <is>
           <t>xlsx-arbre-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>voice_cast</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>voix-roles-v1</t>
         </is>
       </c>
     </row>
@@ -833,7 +844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AV6"/>
+  <dimension ref="A1:AW6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1127,6 +1138,11 @@
           <t>notes</t>
         </is>
       </c>
+      <c r="AW1" t="inlineStr">
+        <is>
+          <t>script</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1151,7 +1167,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Octave est au jardin avec maman. Sa sœur Prune a l'arrosoir. L'eau tombe sur les fleurs. Octave la regarde longtemps. Son ventre se serre. Ses yeux restent sur l'arrosoir. Octave dit : je suis jaloux. Maman écoute. Octave va près de Prune. Il dit : je voudrais demander un tour. Prune dit : encore un peu. Octave attend la réponse. Il compte les gouttes. Il reste les mains sur ses genoux. Puis Prune tend l'arrosoir. Octave a son tour. Il arrose tout doucement. Maman dit : tu as demandé un tour. Tu as attendu la réponse.</t>
+          <t>Octave est au jardin avec maman. Sa sœur Prune a l'arrosoir. L'eau tombe sur les fleurs. Octave la regarde longtemps. Son ventre se serre. Ses yeux restent sur l'arrosoir. Je suis jaloux. Maman écoute. Octave va près de Prune. Je voudrais demander un tour. Encore un peu. Octave attend la réponse. Il compte les gouttes. Il reste les mains sur ses genoux. Puis Prune tend l'arrosoir. Octave a son tour. Il arrose tout doucement. Tu as demandé un tour. Tu as attendu la réponse.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1289,6 +1305,17 @@
         <v>8</v>
       </c>
       <c r="AV2" s="2" t="inlineStr"/>
+      <c r="AW2" t="inlineStr">
+        <is>
+          <t>narrateur|Octave est au jardin avec maman. Sa sœur Prune a l'arrosoir. L'eau tombe sur les fleurs. Octave la regarde longtemps. Son ventre se serre. Ses yeux restent sur l'arrosoir.
+enfant-m|Je suis jaloux. Maman écoute.
+narrateur|Octave va près de Prune.
+narrateur|Je voudrais demander un tour.
+copine|Encore un peu.
+narrateur|Octave attend la réponse. Il compte les gouttes. Il reste les mains sur ses genoux. Puis Prune tend l'arrosoir. Octave a son tour. Il arrose tout doucement.
+maman|Tu as demandé un tour. Tu as attendu la réponse.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1465,6 +1492,11 @@
       <c r="AV3" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>narrateur|Octave veut l'arrosoir. Que fait-il ?</t>
         </is>
       </c>
     </row>
@@ -1633,6 +1665,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>narrateur|Octave a nommé : jaloux. Il a demandé un tour. Il a attendu la réponse.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1791,6 +1828,11 @@
         <v>8</v>
       </c>
       <c r="AV5" s="2" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>narrateur|Octave pose l'arrosoir. Prune reprend un tour. Maman reste près des fleurs.</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1953,6 +1995,11 @@
         <v>8</v>
       </c>
       <c r="AV6" s="2" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -1971,7 +2018,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A2"/>
+  <dimension ref="A1:A3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -1988,6 +2035,13 @@
       <c r="A2" t="inlineStr">
         <is>
           <t>conversion structurelle, prompts de choix alignés, TTS profilé</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-EMO.LEX.009-05.xlsx
+++ b/stories/arbres/ATOM-EMO.LEX.009-05.xlsx
@@ -844,7 +844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW6"/>
+  <dimension ref="A1:AX6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1143,6 +1143,11 @@
           <t>script</t>
         </is>
       </c>
+      <c r="AX1" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1316,6 +1321,7 @@
 maman|Tu as demandé un tour. Tu as attendu la réponse.</t>
         </is>
       </c>
+      <c r="AX2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1499,6 +1505,7 @@
           <t>narrateur|Octave veut l'arrosoir. Que fait-il ?</t>
         </is>
       </c>
+      <c r="AX3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1670,6 +1677,7 @@
           <t>narrateur|Octave a nommé : jaloux. Il a demandé un tour. Il a attendu la réponse.</t>
         </is>
       </c>
+      <c r="AX4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1833,6 +1841,7 @@
           <t>narrateur|Octave pose l'arrosoir. Prune reprend un tour. Maman reste près des fleurs.</t>
         </is>
       </c>
+      <c r="AX5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -2000,6 +2009,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX6" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -2018,7 +2028,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A3"/>
+  <dimension ref="A1:A5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2042,6 +2052,20 @@
       <c r="A3" t="inlineStr">
         <is>
           <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
         </is>
       </c>
     </row>
@@ -2056,7 +2080,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B15"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -2243,6 +2267,18 @@
         </is>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>ids de bruits (vide = silence). Le bruit se joue, puis l'histoire reprend au calme.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/stories/arbres/ATOM-EMO.LEX.009-05.xlsx
+++ b/stories/arbres/ATOM-EMO.LEX.009-05.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B30"/>
+  <dimension ref="A1:B31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -544,7 +544,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Octave demande un tour d'arrosoir</t>
+          <t>L'arrosoir de Sarah</t>
         </is>
       </c>
     </row>
@@ -830,6 +830,18 @@
       <c r="B30" t="inlineStr">
         <is>
           <t>voix-roles-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>fil_rouge</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Aniss a l'arrosoir. Sarah dit qu'elle est jalouse. Elle demande un tour. Elle attend. Elle arrose.</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1184,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Octave est au jardin avec maman. Sa sœur Prune a l'arrosoir. L'eau tombe sur les fleurs. Octave la regarde longtemps. Son ventre se serre. Ses yeux restent sur l'arrosoir. Je suis jaloux. Maman écoute. Octave va près de Prune. Je voudrais demander un tour. Encore un peu. Octave attend la réponse. Il compte les gouttes. Il reste les mains sur ses genoux. Puis Prune tend l'arrosoir. Octave a son tour. Il arrose tout doucement. Tu as demandé un tour. Tu as attendu la réponse.</t>
+          <t>Les tomates sont encore vertes. Une est un peu orange, déjà. Une coccinelle marche sur une feuille. L'arrosoir goutte près du seau. Une goutte. Encore une goutte. La terre est chaude, un peu sèche. Ça sent les plants, tout vert. Un tuteur de bois tient un plant. Il est lisse, un peu gris. Je tiens le seau, Sarah. Aniss a déjà l'arrosoir. La coccinelle est rouge, papa. Oui. Elle a des points noirs. On marche entre les plants. En ce moment, Aniss arrose. L'eau tombe sur les fleurs. Les fleurs sont petites, un peu roses. Sarah regarde l'arrosoir longtemps. Son ventre se serre. Ses yeux restent sur l'arrosoir. Ses mains restent sur ses genoux. Je suis jalouse. Je t'écoute. Jaloux, c'est cette envie. Sarah va près d'Aniss. Je voudrais demander un tour. Encore un peu. On attend la réponse. Sarah attend. Elle compte les gouttes. Une. Deux. Trois. Ses mains restent sur ses genoux. Puis Aniss tend l'arrosoir. C'est ton tour. Merci, Aniss. Sarah a son tour. Elle arrose tout doucement. L'eau fait un cercle sombre, dans la terre. Tu as demandé un tour. Tu as attendu la réponse. Bravo, Sarah. Tu as fait du bon travail. J'ai dit : je suis jalouse. Puis tu as demandé. La coccinelle n'a pas bougé. L'arrosoir goutte encore, un peu.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1233,14 +1245,14 @@
       </c>
       <c r="Z2" s="2" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>slow</t>
         </is>
       </c>
       <c r="AA2" s="2" t="n">
         <v>0.92</v>
       </c>
       <c r="AB2" s="2" t="n">
-        <v>1.18</v>
+        <v>1.28</v>
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
@@ -1312,13 +1324,52 @@
       <c r="AV2" s="2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>narrateur|Octave est au jardin avec maman. Sa sœur Prune a l'arrosoir. L'eau tombe sur les fleurs. Octave la regarde longtemps. Son ventre se serre. Ses yeux restent sur l'arrosoir.
-enfant-m|Je suis jaloux. Maman écoute.
-narrateur|Octave va près de Prune.
-narrateur|Je voudrais demander un tour.
-copine|Encore un peu.
-narrateur|Octave attend la réponse. Il compte les gouttes. Il reste les mains sur ses genoux. Puis Prune tend l'arrosoir. Octave a son tour. Il arrose tout doucement.
-maman|Tu as demandé un tour. Tu as attendu la réponse.</t>
+          <t>narrateur|Les tomates sont encore vertes.
+narrateur|Une est un peu orange, déjà.
+narrateur|Une coccinelle marche sur une feuille.
+narrateur|L'arrosoir goutte près du seau.
+narrateur|Une goutte. Encore une goutte.
+narrateur|La terre est chaude, un peu sèche.
+narrateur|Ça sent les plants, tout vert.
+narrateur|Un tuteur de bois tient un plant.
+narrateur|Il est lisse, un peu gris.
+maman|Je tiens le seau, Sarah.
+papa|Aniss a déjà l'arrosoir.
+enfant-f|La coccinelle est rouge, papa.
+papa|Oui. Elle a des points noirs.
+maman|On marche entre les plants.
+narrateur|En ce moment, Aniss arrose.
+narrateur|L'eau tombe sur les fleurs.
+narrateur|Les fleurs sont petites, un peu roses.
+narrateur|Sarah regarde l'arrosoir longtemps.
+narrateur|Son ventre se serre.
+narrateur|Ses yeux restent sur l'arrosoir.
+narrateur|Ses mains restent sur ses genoux.
+enfant-f|Je suis jalouse.
+maman|Je t'écoute.
+papa|Jaloux, c'est cette envie.
+narrateur|Sarah va près d'Aniss.
+enfant-f|Je voudrais demander un tour.
+enfant-m|Encore un peu.
+maman|On attend la réponse.
+narrateur|Sarah attend.
+narrateur|Elle compte les gouttes.
+narrateur|Une. Deux. Trois.
+narrateur|Ses mains restent sur ses genoux.
+narrateur|Puis Aniss tend l'arrosoir.
+enfant-m|C'est ton tour.
+enfant-f|Merci, Aniss.
+narrateur|Sarah a son tour.
+narrateur|Elle arrose tout doucement.
+narrateur|L'eau fait un cercle sombre, dans la terre.
+maman|Tu as demandé un tour.
+maman|Tu as attendu la réponse.
+papa|Bravo, Sarah.
+papa|Tu as fait du bon travail.
+enfant-f|J'ai dit : je suis jalouse.
+papa|Puis tu as demandé.
+narrateur|La coccinelle n'a pas bougé.
+narrateur|L'arrosoir goutte encore, un peu.</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr"/>
@@ -1346,7 +1397,7 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>Octave veut l'arrosoir. Que fait-il ?</t>
+          <t>Sarah veut l'arrosoir. Que fait-elle ?</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
@@ -1430,7 +1481,7 @@
         <v>0.86</v>
       </c>
       <c r="AB3" s="2" t="n">
-        <v>1.3</v>
+        <v>1.4</v>
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
@@ -1502,7 +1553,8 @@
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>narrateur|Octave veut l'arrosoir. Que fait-il ?</t>
+          <t>narrateur|Sarah veut l'arrosoir.
+narrateur|Que fait-elle ?</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr"/>
@@ -1530,7 +1582,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Octave a nommé : jaloux. Il a demandé un tour. Il a attendu la réponse.</t>
+          <t>Sarah a nommé : jalouse. Elle a demandé un tour. Elle a attendu la réponse. J'ai demandé. J'ai attendu. Oui. Les mains sur les genoux. Bravo. C'est du bon travail. Après, c'est encore mon tour ? On demande. On attend. Oui. On demande un tour. Jaloux, on le dit. La terre est plus sombre, maintenant. Elle sent l'eau, tout frais. Tu as attendu Aniss. Il a dit : encore un peu. Puis il a tendu l'arrosoir. La tomate orange brille un peu.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -1591,14 +1643,14 @@
       </c>
       <c r="Z4" s="2" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>slow</t>
         </is>
       </c>
       <c r="AA4" s="2" t="n">
         <v>0.92</v>
       </c>
       <c r="AB4" s="2" t="n">
-        <v>1.18</v>
+        <v>1.28</v>
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
@@ -1674,7 +1726,22 @@
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>narrateur|Octave a nommé : jaloux. Il a demandé un tour. Il a attendu la réponse.</t>
+          <t>narrateur|Sarah a nommé : jalouse.
+narrateur|Elle a demandé un tour.
+narrateur|Elle a attendu la réponse.
+enfant-f|J'ai demandé. J'ai attendu.
+maman|Oui. Les mains sur les genoux.
+papa|Bravo. C'est du bon travail.
+enfant-m|Après, c'est encore mon tour ?
+papa|On demande. On attend.
+enfant-f|Oui. On demande un tour.
+maman|Jaloux, on le dit.
+narrateur|La terre est plus sombre, maintenant.
+narrateur|Elle sent l'eau, tout frais.
+papa|Tu as attendu Aniss.
+enfant-f|Il a dit : encore un peu.
+maman|Puis il a tendu l'arrosoir.
+narrateur|La tomate orange brille un peu.</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr"/>
@@ -1702,7 +1769,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>Octave pose l'arrosoir. Prune reprend un tour. Maman reste près des fleurs.</t>
+          <t>Sarah pose l'arrosoir. Aniss reprend un tour. Je reste près des fleurs. Le seau est encore un peu lourd. J'ai eu mon tour. Oui. Tu as demandé. L'eau fait des ronds. On écoute les gouttes. Sarah s'assoit près de maman. La terre chaude touche ses chaussures. Tu as attendu la réponse. Mes mains étaient sur mes genoux. C'est le bon geste. Aniss arrose, tout doux. La coccinelle reste sur sa feuille.</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -1763,14 +1830,14 @@
       </c>
       <c r="Z5" s="2" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>slow</t>
         </is>
       </c>
       <c r="AA5" s="2" t="n">
         <v>0.92</v>
       </c>
       <c r="AB5" s="2" t="n">
-        <v>1.18</v>
+        <v>1.28</v>
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
@@ -1838,7 +1905,21 @@
       <c r="AV5" s="2" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>narrateur|Octave pose l'arrosoir. Prune reprend un tour. Maman reste près des fleurs.</t>
+          <t>narrateur|Sarah pose l'arrosoir.
+narrateur|Aniss reprend un tour.
+maman|Je reste près des fleurs.
+papa|Le seau est encore un peu lourd.
+enfant-f|J'ai eu mon tour.
+maman|Oui. Tu as demandé.
+enfant-m|L'eau fait des ronds.
+papa|On écoute les gouttes.
+narrateur|Sarah s'assoit près de maman.
+narrateur|La terre chaude touche ses chaussures.
+papa|Tu as attendu la réponse.
+enfant-f|Mes mains étaient sur mes genoux.
+maman|C'est le bon geste.
+narrateur|Aniss arrose, tout doux.
+narrateur|La coccinelle reste sur sa feuille.</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr"/>
@@ -1866,7 +1947,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>J'étais jalouse. J'ai demandé un tour. Tu as attendu. Bravo. Aniss a eu son tour, aussi. L'arrosoir goutte encore. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -1934,7 +2015,7 @@
         <v>0.88</v>
       </c>
       <c r="AB6" s="2" t="n">
-        <v>1.26</v>
+        <v>1.36</v>
       </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
@@ -2006,7 +2087,11 @@
       <c r="AV6" s="2" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>enfant-f|J'étais jalouse. J'ai demandé un tour.
+maman|Tu as attendu. Bravo.
+papa|Aniss a eu son tour, aussi.
+narrateur|L'arrosoir goutte encore.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr"/>
@@ -2028,7 +2113,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A5"/>
+  <dimension ref="A1:A6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2066,6 +2151,13 @@
       <c r="A5" t="inlineStr">
         <is>
           <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>F-NAR-009 ouverture du monde, fusion agents</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-EMO.LEX.009-05.xlsx
+++ b/stories/arbres/ATOM-EMO.LEX.009-05.xlsx
@@ -1184,12 +1184,12 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Les tomates sont encore vertes. Une est un peu orange, déjà. Une coccinelle marche sur une feuille. L'arrosoir goutte près du seau. Une goutte. Encore une goutte. La terre est chaude, un peu sèche. Ça sent les plants, tout vert. Un tuteur de bois tient un plant. Il est lisse, un peu gris. Je tiens le seau, Sarah. Aniss a déjà l'arrosoir. La coccinelle est rouge, papa. Oui. Elle a des points noirs. On marche entre les plants. En ce moment, Aniss arrose. L'eau tombe sur les fleurs. Les fleurs sont petites, un peu roses. Sarah regarde l'arrosoir longtemps. Son ventre se serre. Ses yeux restent sur l'arrosoir. Ses mains restent sur ses genoux. Je suis jalouse. Je t'écoute. Jaloux, c'est cette envie. Sarah va près d'Aniss. Je voudrais demander un tour. Encore un peu. On attend la réponse. Sarah attend. Elle compte les gouttes. Une. Deux. Trois. Ses mains restent sur ses genoux. Puis Aniss tend l'arrosoir. C'est ton tour. Merci, Aniss. Sarah a son tour. Elle arrose tout doucement. L'eau fait un cercle sombre, dans la terre. Tu as demandé un tour. Tu as attendu la réponse. Bravo, Sarah. Tu as fait du bon travail. J'ai dit : je suis jalouse. Puis tu as demandé. La coccinelle n'a pas bougé. L'arrosoir goutte encore, un peu.</t>
+          <t>Les tomates sont encore vertes. Une est un peu orange, déjà. Une coccinelle marche sur une feuille. L'arrosoir goutte près du seau. Une goutte. Encore une goutte. La terre est chaude, un peu sèche. Ça sent les plants, tout vert. Un tuteur de bois tient un plant. Il est lisse, un peu gris. Je tiens le seau, Sarah. Aniss a déjà l'arrosoir. La coccinelle est rouge, papa. Oui. Elle a des points noirs. On marche entre les plants. En ce moment, Aniss arrose. L'eau tombe sur les fleurs. Les fleurs sont petites, un peu roses. Sarah regarde l'arrosoir longtemps. Son ventre se serre. Ses yeux restent sur l'arrosoir. Ses mains restent sur ses genoux. Je suis jalouse. Je t'écoute. Jaloux, c'est cette envie. Sarah va près d'Aniss. Je voudrais demander un tour. Encore un peu. On attend la réponse. Sarah attend. Elle compte les gouttes. Une. Deux. Trois. Ses mains restent sur ses genoux. Puis Aniss tend l'arrosoir. C'est ton tour. Merci, Aniss. Sarah a son tour. Elle arrose tout doucement. L'eau fait un cercle sombre, dans la terre. Tu as demandé un tour. Tu as attendu la réponse. Bravo, Sarah. J'ai dit : je suis jalouse. Puis tu as demandé. La coccinelle n'a pas bougé. L'arrosoir goutte encore, un peu.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Octave est au jardin avec maman. Sa sœur Prune a l'arrosoir. L'eau tombe sur les fleurs. Octave la regarde longtemps. Son ventre se serre. Ses yeux restent sur l'arrosoir. Octave dit : je suis &lt;emphasis level="moderate"&gt;jaloux&lt;/emphasis&gt;. Maman écoute. Octave va près de Prune. Il dit : je voudrais demander un tour. Prune dit : encore un peu. Octave attend la réponse. Il compte les gouttes. Il reste les mains sur ses genoux. Puis Prune tend l'arrosoir. Octave a son tour. Il arrose tout doucement. Maman dit : tu as demandé un tour. Tu as attendu la réponse.&lt;/prosody&gt;&lt;break time="400ms"/&gt;&lt;/speak&gt;</t>
+          <t>Les tomates sont encore vertes. Une est un peu orange, déjà. Une coccinelle marche sur une feuille. L'arrosoir goutte près du seau. Une goutte. Encore une goutte. La terre est chaude, un peu sèche. Ça sent les plants, tout vert. Un tuteur de bois tient un plant. Il est lisse, un peu gris. Je tiens le seau, Sarah. Aniss a déjà l'arrosoir. La coccinelle est rouge, papa. Oui. Elle a des points noirs. On marche entre les plants. En ce moment, Aniss arrose. L'eau tombe sur les fleurs. Les fleurs sont petites, un peu roses. Sarah regarde l'arrosoir longtemps. Son ventre se serre. Ses yeux restent sur l'arrosoir. Ses mains restent sur ses genoux. Je suis jalouse. Je t'écoute. Jaloux, c'est cette envie. Sarah va près d'Aniss. Je voudrais demander un tour. Encore un peu. On attend la réponse. Sarah attend. Elle compte les gouttes. Une. Deux. Trois. Ses mains restent sur ses genoux. Puis Aniss tend l'arrosoir. C'est ton tour. Merci, Aniss. Sarah a son tour. Elle arrose tout doucement. L'eau fait un cercle sombre, dans la terre. Tu as demandé un tour. Tu as attendu la réponse. Bravo, Sarah. J'ai dit : je suis jalouse. Puis tu as demandé. La coccinelle n'a pas bougé. L'arrosoir goutte encore, un peu.</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
@@ -1365,14 +1365,12 @@
 maman|Tu as demandé un tour.
 maman|Tu as attendu la réponse.
 papa|Bravo, Sarah.
-papa|Tu as fait du bon travail.
 enfant-f|J'ai dit : je suis jalouse.
 papa|Puis tu as demandé.
 narrateur|La coccinelle n'a pas bougé.
 narrateur|L'arrosoir goutte encore, un peu.</t>
         </is>
       </c>
-      <c r="AX2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1402,7 +1400,7 @@
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="medium"&gt;Octave veut l'arrosoir. Que fait-il ?&lt;/prosody&gt;&lt;break time="250ms"/&gt;&lt;/speak&gt;</t>
+          <t>Sarah veut l'arrosoir. Que fait-elle ?</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
@@ -1557,7 +1555,6 @@
 narrateur|Que fait-elle ?</t>
         </is>
       </c>
-      <c r="AX3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1582,12 +1579,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Sarah a nommé : jalouse. Elle a demandé un tour. Elle a attendu la réponse. J'ai demandé. J'ai attendu. Oui. Les mains sur les genoux. Bravo. C'est du bon travail. Après, c'est encore mon tour ? On demande. On attend. Oui. On demande un tour. Jaloux, on le dit. La terre est plus sombre, maintenant. Elle sent l'eau, tout frais. Tu as attendu Aniss. Il a dit : encore un peu. Puis il a tendu l'arrosoir. La tomate orange brille un peu.</t>
+          <t>Sarah a nommé : jalouse. Elle a demandé un tour. Elle a attendu la réponse. J'ai demandé. J'ai attendu. Oui. Les mains sur les genoux. Après, c'est encore mon tour ? On demande. On attend. Oui. On demande un tour. Jaloux, on le dit. La terre est plus sombre, maintenant. Elle sent l'eau, tout frais. Tu as attendu Aniss. Il a dit : encore un peu. Puis il a tendu l'arrosoir. La tomate orange brille un peu.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Octave a nommé : &lt;emphasis level="moderate"&gt;jaloux&lt;/emphasis&gt;. Il a demandé un tour. Il a attendu la réponse.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>Sarah a nommé : jalouse. Elle a demandé un tour. Elle a attendu la réponse. J'ai demandé. J'ai attendu. Oui. Les mains sur les genoux. Après, c'est encore mon tour ? On demande. On attend. Oui. On demande un tour. Jaloux, on le dit. La terre est plus sombre, maintenant. Elle sent l'eau, tout frais. Tu as attendu Aniss. Il a dit : encore un peu. Puis il a tendu l'arrosoir. La tomate orange brille un peu.</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -1731,7 +1728,6 @@
 narrateur|Elle a attendu la réponse.
 enfant-f|J'ai demandé. J'ai attendu.
 maman|Oui. Les mains sur les genoux.
-papa|Bravo. C'est du bon travail.
 enfant-m|Après, c'est encore mon tour ?
 papa|On demande. On attend.
 enfant-f|Oui. On demande un tour.
@@ -1744,7 +1740,6 @@
 narrateur|La tomate orange brille un peu.</t>
         </is>
       </c>
-      <c r="AX4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1774,7 +1769,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Octave pose l'arrosoir. Prune reprend un tour. Maman reste près des fleurs.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>Sarah pose l'arrosoir. Aniss reprend un tour. Je reste près des fleurs. Le seau est encore un peu lourd. J'ai eu mon tour. Oui. Tu as demandé. L'eau fait des ronds. On écoute les gouttes. Sarah s'assoit près de maman. La terre chaude touche ses chaussures. Tu as attendu la réponse. Mes mains étaient sur mes genoux. C'est le bon geste. Aniss arrose, tout doux. La coccinelle reste sur sa feuille.</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1922,7 +1917,6 @@
 narrateur|La coccinelle reste sur sa feuille.</t>
         </is>
       </c>
-      <c r="AX5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1947,12 +1941,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>J'étais jalouse. J'ai demandé un tour. Tu as attendu. Bravo. Aniss a eu son tour, aussi. L'arrosoir goutte encore. L'histoire est finie.</t>
+          <t>J'étais jalouse. J'ai demandé un tour. Tu as attendu. Bravo. Aniss a eu son tour, aussi. L'arrosoir goutte encore.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="low"&gt;L'histoire est finie.&lt;/prosody&gt;&lt;break time="600ms"/&gt;&lt;/speak&gt;</t>
+          <t>J'étais jalouse. J'ai demandé un tour. Tu as attendu. Bravo. Aniss a eu son tour, aussi. L'arrosoir goutte encore.</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -2090,11 +2084,9 @@
           <t>enfant-f|J'étais jalouse. J'ai demandé un tour.
 maman|Tu as attendu. Bravo.
 papa|Aniss a eu son tour, aussi.
-narrateur|L'arrosoir goutte encore.
-narrateur|L'histoire est finie.</t>
-        </is>
-      </c>
-      <c r="AX6" t="inlineStr"/>
+narrateur|L'arrosoir goutte encore.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -2113,7 +2105,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A6"/>
+  <dimension ref="A1:A7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2158,6 +2150,13 @@
       <c r="A6" t="inlineStr">
         <is>
           <t>F-NAR-009 ouverture du monde, fusion agents</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>F-NAR-008 récit, pas une leçon en puces</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-EMO.LEX.009-05.xlsx
+++ b/stories/arbres/ATOM-EMO.LEX.009-05.xlsx
@@ -683,7 +683,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Octave, Prune, maman</t>
+          <t>Sarah, Aniss, papa, maman</t>
         </is>
       </c>
     </row>
